--- a/fantasy_draft_2026.xlsx
+++ b/fantasy_draft_2026.xlsx
@@ -988,7 +988,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>VERIFIED FROM SLEEPER — "GovSmart Gridiron":  12-team snake  •  0.5 PPR  •  6-PT passing TDs  •  $100 FAAB  •  your slot #3  •  draft Fri Sep 4, 5:30 PM ET, 90s pick timer.   ROSTER: QB / RB / RB / WR / WR / TE / FLEX / DEF + 4 BENCH — only 12 rounds, NO KICKER, and a DEFENSE is a required starter. 2 IR slots let you stash an injured guy. 6-pt pass TDs lift EVERY QB including the streamer, so the elite QB's edge grows only ~7 pts ALL SEASON (measured on 2025 data) — WAIT ON QB until round 9+, and prefer high-volume pocket passers over dual-threats.</t>
+          <t>VERIFIED FROM SLEEPER — "GovSmart Gridiron":  12-team snake  •  0.5 PPR  •  6-PT passing TDs  •  $100 FAAB  •  your slot #3  •  draft Fri Sep 4, 5:30 PM ET, 90s pick timer.   ROSTER: QB / RB / RB / WR / WR / TE / FLEX / DEF + 4 BENCH — only 12 rounds, NO KICKER, and a DEFENSE is a required starter. 2 IR slots let you stash an injured guy. 6-pt pass TDs lift EVERY QB including the streamer, so the elite QB's edge grows only 7-19 pts ALL SEASON (measured across 2024+2025) — WAIT ON QB until round 9+, then take the highest PASSING-TD volume left (the rule pays 2 pts per passing TD and nothing for rushing).</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>QB, MEASURED (2025 nflverse, re-scored to 6-pt): the rule lifts the STREAMER from 17.4 to 20.9 pts/g and the top-6 from 20.7 to 24.5 — the elite QB's ADVANTAGE grows just 0.4 pts/g (~7 pts a season). Rushing TDs are already 6 pts in every format, so pocket passers gain most: Stafford +92, Goff +68, Maye +62 vs Allen +50, Lamar +42. Wait until round 9.</t>
+          <t>QB, MEASURED (nflverse 2024+2025, re-scored to 6-pt): the rule lifts the STREAMER from 17.4 to 20.9 pts/g and the top-6 from 20.7 to 24.5 — the elite QB's ADVANTAGE grows only 7-19 pts across a WHOLE SEASON (median 12.5 over 2 seasons x 3 replacement ranks). For scale, value over replacement: best QB ~60, best TE ~113, best WR ~117, best RB ~227. The rule pays exactly 2 pts per PASSING TD and nothing for rushing, so judge a QB on passing-TD volume, not on being a dual-threat. Wait until round 9.</t>
         </is>
       </c>
     </row>
@@ -8002,7 +8002,7 @@
       </c>
       <c r="K20" s="60" t="inlineStr">
         <is>
-          <t>6-PT PASS TDs — WHAT THE DATA ACTUALLY SAYS: the rule lifts every QB, streamer included, so the elite QB's edge over a streamer grows only ~7 pts across a whole season. And because rushing TDs are already 6 pts in EVERY format, dual-threats gain the LEAST: Stafford +92 / Goff +68 / Maye +62 vs Allen +50 / Lamar +42. Wait on QB until round 9, then take the highest-volume passer left. Source: build_edge.py on 2025 nflverse.</t>
+          <t>6-PT PASS TDs — WHAT THE DATA ACTUALLY SAYS: the rule lifts every QB, streamer included, so the elite QB's edge over a streamer grows only 7-19 pts across a WHOLE season (median 12.5, measured over 2024+2025 x 3 replacement ranks). The rule pays exactly 2 pts per PASSING TD and nothing extra for rushing, so judge on passing-TD volume — 2025: Stafford +92, Goff +68, Maye +62; 2024: Burrow +86, Mayfield +82, Jackson +82. Wait on QB until round 9. Source: build_edge.py on nflverse.</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>46 and 30 pass TDs in 2025 = +92 and +60 pts from the 6-pt rule, going 50+ picks after Allen.</t>
+          <t>46 and 30 pass TDs in 2025 = +92 and +60 pts from the 6-pt rule, going 50+ picks after Allen. Judge QBs on passing-TD volume, not rushing reputation.</t>
         </is>
       </c>
       <c r="C8" s="64" t="n"/>

--- a/fantasy_draft_2026.xlsx
+++ b/fantasy_draft_2026.xlsx
@@ -1506,7 +1506,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BIG BOARD — 2026 Half-PPR (Top 120)</t>
+          <t>BIG BOARD — 2026 Half-PPR (Top 129)</t>
         </is>
       </c>
     </row>

--- a/fantasy_draft_2026.xlsx
+++ b/fantasy_draft_2026.xlsx
@@ -1460,7 +1460,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>QB, MEASURED (nflverse 2024+2025, re-scored to 6-pt): the rule lifts the STREAMER from 17.4 to 20.9 pts/g and the top-6 from 20.7 to 24.5 — the elite QB's ADVANTAGE grows only 7-19 pts across a WHOLE SEASON (median 12.5 over 2 seasons x 3 replacement ranks). For scale, value over replacement: best QB ~60, best TE ~113, best WR ~117, best RB ~227. The rule pays exactly 2 pts per PASSING TD and nothing for rushing, so judge a QB on passing-TD volume, not on being a dual-threat. Wait until round 9.</t>
+          <t>QB, MEASURED (nflverse 2024+2025, re-scored to 6-pt): the rule lifts the STREAMER too, so a top-6 QB's ADVANTAGE grows only 7-19 pts across a WHOLE SEASON (median 12.5 over 2 seasons x 3 replacement ranks). The single best QB is much noisier (-4 to +34) and not worth planning around. The real reason to wait is value over replacement: best QB ~53 pts, best TE ~113, best WR ~117, best RB ~228. The rule pays exactly 2 pts per PASSING TD and nothing extra for rushing, so judge a QB on passing-TD volume. Wait until round 9.</t>
         </is>
       </c>
     </row>
